--- a/sheet_template.xlsx
+++ b/sheet_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Intern_project\E-Commerce_website\drone-e-commerce-platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9096AAC-74B2-48A3-AFB3-42ADEED0F426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C1C68E-890A-4A02-B400-10E2D154AD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>Sl.NO</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>QTY</t>
   </si>
   <si>
@@ -43,6 +40,9 @@
   </si>
   <si>
     <t>HDS-GRD-X500-002</t>
+  </si>
+  <si>
+    <t>Model Number</t>
   </si>
 </sst>
 </file>
@@ -386,10 +386,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:4">
@@ -397,7 +397,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1">
         <v>20</v>
